--- a/CBT_2022_4회/산업안전기사_2022_4회_문항등록.xlsx
+++ b/CBT_2022_4회/산업안전기사_2022_4회_문항등록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="AG7" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;무(無)의 원칙&lt;/strong&gt;이다. &lt;strong&gt;「근원적으로 없앤다」&lt;/strong&gt;는 말이 곧 무의 원칙이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;무재해운동의 기본이념 3원칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원칙&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무(無)의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;잠재위험요인을 뿌리에서부터 없애 산업재해를 0 으로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;참가의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전원이 참가해 각자의 자리에서 문제를 푼다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;선취(안전제일)의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;행동하기 전에 위험을 미리 알아채 없앤다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;무(無)의 원칙&lt;/strong&gt;이다. &lt;strong&gt;「근원적으로 없앤다」&lt;/strong&gt;는 말이 곧 무의 원칙이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;무재해운동의 기본이념 3원칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원칙&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무(無)의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;잠재위험요인을 뿌리에서부터 없애 산업재해를 0으로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;참가의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전원이 참가해 각자의 자리에서 문제를 푼다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;선취(안전제일)의 원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;행동하기 전에 위험을 미리 알아채 없앤다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH7" s="32" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="U8" s="32" t="inlineStr">
         <is>
-          <t>다음 중 재해예방을 위한 시정책인 「3E에 해당하지 않는 것은?</t>
+          <t>다음 중 재해예방을 위한 시정책인 「3E」에 해당하지 않는 것은?</t>
         </is>
       </c>
       <c r="V8" s="32" t="inlineStr"/>
@@ -2092,17 +2092,17 @@
       </c>
       <c r="AG8" s="32" t="inlineStr">
         <is>
-          <t>셋은 &lt;strong&gt;Engineering · Education · Enforcement&lt;/strong&gt;다. &lt;strong&gt;Energy 는 들지 않는다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;하비(Harvey)의 3E&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;E&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Engineering&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기술적 대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안전설계 · 작업행정 개선 · 환경설비 개선&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Education&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;교육적 대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안전교육 · 훈련&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Enforcement&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관리적(규제적) 대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;규정 제정 · 지시 · 감독 · 이행 독려&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Energy&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3E 가 아니다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>셋은 &lt;strong&gt;Engineering · Education · Enforcement&lt;/strong&gt;다. &lt;strong&gt;Energy는 들지 않는다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;하비(Harvey)의 3E&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;E&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Engineering&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기술적 대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안전설계 · 작업행정 개선 · 환경설비 개선&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Education&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;교육적 대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안전교육 · 훈련&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Enforcement&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관리적(규제적) 대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;규정 제정 · 지시 · 감독 · 이행 독려&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Energy&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3E가 아니다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH8" s="32" t="inlineStr">
         <is>
-          <t>① Education 은 3E 의 하나다.&lt;br&gt;③ Engineering 도 그렇다.&lt;br&gt;④ Enforcement 도 그렇다.</t>
+          <t>① Education은 3E의 하나다.&lt;br&gt;③ Engineering 도 그렇다.&lt;br&gt;④ Enforcement 도 그렇다.</t>
         </is>
       </c>
       <c r="AI8" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;재해예방의 3E&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「고치고(기술) · 가르치고(교육) · 지키게 한다(관리)」&lt;/strong&gt; 셋이다 — &lt;strong&gt;여기에 Environment(환경)를 더하면 4E&lt;/strong&gt;다. &lt;strong&gt;Energy 는 어느 쪽에도 없다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;Engineering · Education · Enforcement&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;재해예방의 3E&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「고치고(기술) · 가르치고(교육) · 지키게 한다(관리)」&lt;/strong&gt; 셋이다 — &lt;strong&gt;여기에 Environment(환경)를 더하면 4E&lt;/strong&gt;다. &lt;strong&gt;Energy는 어느 쪽에도 없다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;Engineering · Education · Enforcement&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2871,7 +2871,7 @@
       </c>
       <c r="AH14" s="32" t="inlineStr">
         <is>
-          <t>② Rationalization 은 방어기제의 이름이다.&lt;br&gt;③ Economy 욕구는 ERG 에 없다.&lt;br&gt;④ Environment 욕구도 없다.</t>
+          <t>② Rationalization은 방어기제의 이름이다.&lt;br&gt;③ Economy 욕구는 ERG에 없다.&lt;br&gt;④ Environment 욕구도 없다.</t>
         </is>
       </c>
       <c r="AI14" s="32" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AG18" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;내열성&lt;/strong&gt;은 성능기준 항목이 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전모의 성능시험 항목&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내관통성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;AE·ABE 종은 관통거리 9.5 [mm] 이하, AB 종은 11.1 [mm] 이하&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;충격흡수성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;전달충격력 4,450 [N] 미만&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내전압성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;AE·ABE 종 — 교류 20 [kV] 에서 1분간, 누설전류 10 [mA] 이하&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내수성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;AE·ABE 종 — 질량증가율 1% 미만&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난연성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;불꽃을 내며 5초 이상 타지 않을 것&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;턱끈풀림&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;150 [N] 이상 250 [N] 이하에서 풀릴 것&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내열성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;성능기준 항목이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;내열성&lt;/strong&gt;은 성능기준 항목이 아니다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전모의 성능시험 항목&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내관통성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;AE·ABE 종은 관통거리 9.5 [mm] 이하, AB 종은 11.1 [mm] 이하&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;충격흡수성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;전달충격력 4,450 [N] 미만&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내전압성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;AE·ABE 종 — 교류 20 [kV]에서 1분간, 누설전류 10 [mA] 이하&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내수성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;AE·ABE 종 — 질량증가율 1% 미만&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난연성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;불꽃을 내며 5초 이상 타지 않을 것&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;턱끈풀림&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;150 [N] 이상 250 [N] 이하에서 풀릴 것&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내열성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;성능기준 항목이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH18" s="32" t="inlineStr">
@@ -3640,17 +3640,17 @@
       </c>
       <c r="AG20" s="32" t="inlineStr">
         <is>
-          <t>연근로시간은 $1 {,} 000 \times 48 \times 50 \times 0.97 = 2 {,} 328 {,} 000$ 시간이다. $\dfrac{100}{2 {,} 328 {,} 000} \times 10^{6} \fallingdotseq 42.96$ 이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;도수율의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 총 근로시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000 × 48 × 50 = 2,400,000 시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 결근 3% 를 뺀다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2,400,000 × 0.97 = 2,328,000 시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;여기서 갈린다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③ 도수율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{100}{2 {,} 328 {,} 000} \times 10^{6} = 42.96$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;결근을 빼지 않으면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;41.67&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③으로 끌린다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>연근로시간은 $1 {,} 000 \times 48 \times 50 \times 0.97 = 2 {,} 328 {,} 000$ 시간이다. $\dfrac{100}{2 {,} 328 {,} 000} \times 10^{6} \fallingdotseq 42.96$이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;도수율의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 총 근로시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000 × 48 × 50 = 2,400,000 시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 결근 3%를 뺀다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2,400,000 × 0.97 = 2,328,000 시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;여기서 갈린다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③ 도수율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{100}{2 {,} 328 {,} 000} \times 10^{6} = 42.96$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;결근을 빼지 않으면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;41.67&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③으로 끌린다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH20" s="32" t="inlineStr">
         <is>
-          <t>① 31.67 은 계산과 맞지 않는다.&lt;br&gt;② 32.96 도 그렇다.&lt;br&gt;③ 41.67 은 결근 3% 를 빼지 않은 값이다.</t>
+          <t>① 31.67은 계산과 맞지 않는다.&lt;br&gt;② 32.96 도 그렇다.&lt;br&gt;③ 41.67은 결근 3%를 빼지 않은 값이다.</t>
         </is>
       </c>
       <c r="AI20" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;도수율&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「실제로 일한 시간」이 분모&lt;/strong&gt;다 — &lt;strong&gt;결근한 3% 는 일하지 않았으므로 빼야&lt;/strong&gt; 한다. &lt;strong&gt;빼지 않은 값이 보기에 함께 놓여&lt;/strong&gt; 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;결근시간은 빼고 셈한다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;도수율&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「실제로 일한 시간」이 분모&lt;/strong&gt;다 — &lt;strong&gt;결근한 3%는 일하지 않았으므로 빼야&lt;/strong&gt; 한다. &lt;strong&gt;빼지 않은 값이 보기에 함께 놓여&lt;/strong&gt; 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;결근시간은 빼고 셈한다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3898,12 +3898,12 @@
       </c>
       <c r="AG22" s="32" t="inlineStr">
         <is>
-          <t>연근로시간은 $300 \times 48 \times 50 = 720 {,} 000$ 시간이다. $\dfrac{800}{720 {,} 000} \times 1 {,} 000 \fallingdotseq 1.11$ 이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;강도율의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{근로손실일수}}{\text{연근로시간수}} \times 1 {,} 000$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연근로시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;300 × 48 × 50 = 720,000 시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;800 ÷ 720,000 × 1,000 = 1.11&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;재해건수 200건&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;강도율의 셈에는 쓰이지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;도수율에 쓰인다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>연근로시간은 $300 \times 48 \times 50 = 720 {,} 000$ 시간이다. $\dfrac{800}{720 {,} 000} \times 1 {,} 000 \fallingdotseq 1.11$이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;강도율의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{근로손실일수}}{\text{연근로시간수}} \times 1 {,} 000$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연근로시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;300 × 48 × 50 = 720,000 시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;800 ÷ 720,000 × 1,000 = 1.11&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;재해건수 200건&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;강도율의 셈에는 쓰이지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;도수율에 쓰인다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH22" s="32" t="inlineStr">
         <is>
-          <t>② 0.90 은 계산과 맞지 않는다.&lt;br&gt;③ 0.16 도 그렇다.&lt;br&gt;④ 0.84 도 그렇다.</t>
+          <t>② 0.90은 계산과 맞지 않는다.&lt;br&gt;③ 0.16 도 그렇다.&lt;br&gt;④ 0.84 도 그렇다.</t>
         </is>
       </c>
       <c r="AI22" s="32" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AG25" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;규칙 기반 착오&lt;/strong&gt;다. &lt;strong&gt;몸에 밴 규칙(우측 통행)을 그 규칙이 통하지 않는 곳에 그대로 적용&lt;/strong&gt; 했다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;라스무센·리즌의 휴먼에러 분류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;숙련 기반 에러&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;익숙한 동작을 하다 실수하거나 잊는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;실수(slip) · 건망증(lapse)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;규칙 기반 착오&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아는 규칙을 잘못 적용한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;우측통행 나라의 규칙을 좌측통행 나라에서&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지식 기반 착오&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아는 것이 모자라 판단을 그르친다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;처음 겪는 상황&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위반(violation)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;알면서 일부러 어긴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;규칙 기반 착오&lt;/strong&gt;다. &lt;strong&gt;몸에 밴 규칙(우측 통행)을 그 규칙이 통하지 않는 곳에 그대로 적용&lt;/strong&gt;했다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;라스무센·리즌의 휴먼에러 분류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;숙련 기반 에러&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;익숙한 동작을 하다 실수하거나 잊는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;실수(slip) · 건망증(lapse)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;규칙 기반 착오&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아는 규칙을 잘못 적용한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;우측통행 나라의 규칙을 좌측통행 나라에서&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지식 기반 착오&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;아는 것이 모자라 판단을 그르친다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;처음 겪는 상황&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위반(violation)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;알면서 일부러 어긴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH25" s="32" t="inlineStr">
@@ -4611,7 +4611,7 @@
         <v>1</v>
       </c>
       <c r="Q28" s="32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R28" s="32" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       <c r="S28" s="32" t="inlineStr"/>
       <c r="T28" s="32" t="inlineStr">
         <is>
-          <t>원본 시행일 2012.03.04 (1회 출제) | 자동판정 빈출도1 · 개념형 · 난이도1</t>
+          <t>원본 시행일 2012.03.04 (1회 출제) | 자동판정 빈출도1 · 개념형 · 난이도2</t>
         </is>
       </c>
       <c r="U28" s="32" t="inlineStr">
@@ -4629,7 +4629,11 @@
           <t>체계 설계 과정의 주요 단계가 다음과 같을 때 인간ㆍ하드웨어ㆍ소프트웨어의 기능 할당, 인간성능 요건 명세, 직무분석, 작업설계 등의 활동을 하는 단계는?</t>
         </is>
       </c>
-      <c r="V28" s="32" t="inlineStr"/>
+      <c r="V28" s="32" t="inlineStr">
+        <is>
+          <t>목표 및 성능 명세 결정 · 체계의 정의 · 기본 설계&lt;br&gt;계면 설계 · 촉진물 설계 · 시험 및 평가</t>
+        </is>
+      </c>
       <c r="W28" s="32" t="inlineStr"/>
       <c r="X28" s="32" t="inlineStr">
         <is>
@@ -4922,7 +4926,7 @@
       </c>
       <c r="AG30" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;「전혀 발생하지 않는(impossible)」&lt;/strong&gt;이라는 등급은 없다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;MIL-STD-882B 의 발생빈도 다섯 등급&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;등급&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;자주 발생하는(frequent)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보통 발생하는(reasonably probable)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가끔 발생하는(occasional)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;거의 발생하지 않는(remote)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;극히 발생하지 않을 것 같은(extremely improbable)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전혀 발생하지 않는(impossible)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;없는 등급&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;「전혀 발생하지 않는(impossible)」&lt;/strong&gt;이라는 등급은 없다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;MIL-STD-882B의 발생빈도 다섯 등급&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;등급&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;자주 발생하는(frequent)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;보통 발생하는(reasonably probable)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가끔 발생하는(occasional)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;거의 발생하지 않는(remote)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;극히 발생하지 않을 것 같은(extremely improbable)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전혀 발생하지 않는(impossible)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;없는 등급&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH30" s="32" t="inlineStr">
@@ -5061,7 +5065,7 @@
       </c>
       <c r="AI31" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FMEA 의 고장평점법&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;다섯 요소가 모두 「고장」에 관한 말&lt;/strong&gt;이다 — &lt;strong&gt;중요도 · 범위 · 빈도 · 방지 가능성 · 신규설계&lt;/strong&gt;. &lt;strong&gt;「생산능력」은 고장과 무관&lt;/strong&gt; 하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;생산능력은 평가요소가 아니다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FMEA의 고장평점법&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;다섯 요소가 모두 「고장」에 관한 말&lt;/strong&gt;이다 — &lt;strong&gt;중요도 · 범위 · 빈도 · 방지 가능성 · 신규설계&lt;/strong&gt;. &lt;strong&gt;「생산능력」은 고장과 무관&lt;/strong&gt;하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;생산능력은 평가요소가 아니다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5309,7 +5313,7 @@
       </c>
       <c r="AG33" s="32" t="inlineStr">
         <is>
-          <t>설비고장도수율은 $\dfrac{\text{설비고장건수}}{\text{설비가동시간}}$ 이다. &lt;strong&gt;분자와 분모가 뒤바뀌어&lt;/strong&gt; 있다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;보전효과의 평가요소&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;설비고장도수율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{설비고장건수}}{\text{설비가동시간}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;뒤집어 놓은 것이 함정&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;설비고장강도율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{설비고장 정지시간}}{\text{설비가동시간}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;제품단위당 보전비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{총보전비}}{\text{제품수량}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;운전 1시간당 보전비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{총보전비}}{\text{설비운전시간}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계획공사율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{계획공사공수}}{\text{전공수}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>설비고장도수율은 $\dfrac{\text{설비고장건수}}{\text{설비가동시간}}$이다. &lt;strong&gt;분자와 분모가 뒤바뀌어&lt;/strong&gt; 있다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;보전효과의 평가요소&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;설비고장도수율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{설비고장건수}}{\text{설비가동시간}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;뒤집어 놓은 것이 함정&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;설비고장강도율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{설비고장 정지시간}}{\text{설비가동시간}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;제품단위당 보전비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{총보전비}}{\text{제품수량}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;운전 1시간당 보전비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{총보전비}}{\text{설비운전시간}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계획공사율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{계획공사공수}}{\text{전공수}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH33" s="32" t="inlineStr">
@@ -5700,12 +5704,12 @@
       </c>
       <c r="AG36" s="32" t="inlineStr">
         <is>
-          <t>$S = M - E \pm R \pm C - W = 900 - 2 {,} 250 + 1 {,} 900 + 80 - 480 = 150$ [Btu] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;열균형 방정식&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;값&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;S&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;열축적&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;구하는 값&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;M&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대사량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;900&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;증발에 의한 열손실&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−2,250&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;복사에 의한 열이득&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;+1,900&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;C&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대류에 의한 열이득&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;+80&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;W&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;한 일&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−480&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$S = M - E \pm R \pm C - W$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$S = M - E \pm R \pm C - W = 900 - 2 {,} 250 + 1 {,} 900 + 80 - 480 = 150$ [Btu]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;열균형 방정식&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;값&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;S&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;열축적&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;구하는 값&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;M&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대사량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;900&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;증발에 의한 열손실&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−2,250&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;복사에 의한 열이득&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;+1,900&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;C&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대류에 의한 열이득&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;+80&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;W&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;한 일&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−480&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$S = M - E \pm R \pm C - W$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH36" s="32" t="inlineStr">
         <is>
-          <t>① 100 [Btu] 는 계산과 맞지 않는다.&lt;br&gt;③ 200 [Btu] 도 그렇다.&lt;br&gt;④ 250 [Btu] 도 그렇다.</t>
+          <t>① 100 [Btu]는 계산과 맞지 않는다.&lt;br&gt;③ 200 [Btu] 도 그렇다.&lt;br&gt;④ 250 [Btu] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI36" s="32" t="inlineStr">
@@ -6474,17 +6478,17 @@
       </c>
       <c r="AG42" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;HSI(열압박지수)&lt;/strong&gt;는 &lt;strong&gt;더위&lt;/strong&gt;를 나타내는 지수다. 음량과 관계없다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;음량의 척도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;척도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;dB(데시벨)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;음압수준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;phon(폰)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000 [Hz] 순음의 [dB] 값에 맞춘 음량수준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;등감곡선&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;sone(손)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000 [Hz], 40 [dB] 을 1 sone 으로 한 감각적 음량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;10 [phon] 오를 때마다 2배&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;PNdB · PNC · NRN&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;소음의 성가심 정도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;HSI&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;열압박지수(Heat Stress Index)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;더위의 척도&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;HSI(열압박지수)&lt;/strong&gt;는 &lt;strong&gt;더위&lt;/strong&gt;를 나타내는 지수다. 음량과 관계없다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;음량의 척도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;척도&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;dB(데시벨)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;음압수준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;phon(폰)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000 [Hz] 순음의 [dB] 값에 맞춘 음량수준&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;등감곡선&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;sone(손)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000 [Hz], 40 [dB]을 1 sone으로 한 감각적 음량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;10 [phon] 오를 때마다 2배&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;PNdB · PNC · NRN&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;소음의 성가심 정도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;HSI&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;열압박지수(Heat Stress Index)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;더위의 척도&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH42" s="32" t="inlineStr">
         <is>
-          <t>① dB 은 음압수준의 단위다.&lt;br&gt;③ phon 은 음량수준의 단위다.&lt;br&gt;④ sone 은 감각적 음량의 단위다.</t>
+          <t>① dB은 음압수준의 단위다.&lt;br&gt;③ phon은 음량수준의 단위다.&lt;br&gt;④ sone은 감각적 음량의 단위다.</t>
         </is>
       </c>
       <c r="AI42" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;음량의 척도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;셋은 소리, 하나는 더위&lt;/strong&gt;다 — &lt;strong&gt;HSI 의 H 가 Heat&lt;/strong&gt;라는 것만 알면 곧 갈린다. &lt;strong&gt;phon 과 sone 의 관계(10 [phon] 마다 2배)&lt;/strong&gt;도 함께 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;HSI 는 열압박지수&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;음량의 척도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;셋은 소리, 하나는 더위&lt;/strong&gt;다 — &lt;strong&gt;HSI의 H가 Heat&lt;/strong&gt;라는 것만 알면 곧 갈린다. &lt;strong&gt;phon과 sone의 관계(10 [phon] 마다 2배)&lt;/strong&gt;도 함께 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;HSI는 열압박지수&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7124,7 +7128,7 @@
       </c>
       <c r="AH47" s="32" t="inlineStr">
         <is>
-          <t>② 제2종은 12 [mm²] 가 아니라 16 [mm²] 이상이다.&lt;br&gt;③ 제3종은 5 [mm²] 가 아니라 2.5 [mm²] 이상이다.&lt;br&gt;④ 특별 제3종도 3.5 [mm²] 가 아니라 2.5 [mm²] 이상이다.</t>
+          <t>② 제2종은 12 [mm²]가 아니라 16 [mm²] 이상이다.&lt;br&gt;③ 제3종은 5 [mm²]가 아니라 2.5 [mm²] 이상이다.&lt;br&gt;④ 특별 제3종도 3.5 [mm²]가 아니라 2.5 [mm²] 이상이다.</t>
         </is>
       </c>
       <c r="AI47" s="32" t="inlineStr">
@@ -8027,7 +8031,7 @@
       </c>
       <c r="AH54" s="32" t="inlineStr">
         <is>
-          <t>① 50 [lux] 는 기준에 못 미친다.&lt;br&gt;③ 90 [lux] 는 기준값이 아니다.&lt;br&gt;④ 100 [lux] 도 그렇다.</t>
+          <t>① 50 [lux]는 기준에 못 미친다.&lt;br&gt;③ 90 [lux]는 기준값이 아니다.&lt;br&gt;④ 100 [lux] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI54" s="32" t="inlineStr">
@@ -8156,7 +8160,7 @@
       </c>
       <c r="AH55" s="32" t="inlineStr">
         <is>
-          <t>② 456 ~ 458 [℃] 는 값이 맞지 않는다.&lt;br&gt;③ 506 ~ 508 [℃] 도 그렇다.&lt;br&gt;④ 556 ~ 558 [℃] 도 그렇다.</t>
+          <t>② 456 ~ 458 [℃]는 값이 맞지 않는다.&lt;br&gt;③ 506 ~ 508 [℃] 도 그렇다.&lt;br&gt;④ 556 ~ 558 [℃] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI55" s="32" t="inlineStr">
@@ -8285,12 +8289,12 @@
       </c>
       <c r="AH56" s="32" t="inlineStr">
         <is>
-          <t>① 1.2 [m] 는 사람이 넘기 쉽다.&lt;br&gt;② 1.5 [m] 도 기준에 못 미친다.&lt;br&gt;④ 2 [m] 는 기준보다 높다.</t>
+          <t>① 1.2 [m]는 사람이 넘기 쉽다.&lt;br&gt;② 1.5 [m] 도 기준에 못 미친다.&lt;br&gt;④ 2 [m]는 기준보다 높다.</t>
         </is>
       </c>
       <c r="AI56" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;산업용 로봇의 방호&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1.8 [m] 는 어른이 넘어 들어가기 어려운 높이&lt;/strong&gt;다 — &lt;strong&gt;로봇의 팔은 예고 없이 빠르게 움직이므로 사람이 반경 안에 들어가지 못하게&lt;/strong&gt; 하는 것이 최선이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;로봇 방책은 1.8 [m] 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;산업용 로봇의 방호&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1.8 [m]는 어른이 넘어 들어가기 어려운 높이&lt;/strong&gt;다 — &lt;strong&gt;로봇의 팔은 예고 없이 빠르게 움직이므로 사람이 반경 안에 들어가지 못하게&lt;/strong&gt; 하는 것이 최선이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;로봇 방책은 1.8 [m] 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8409,7 +8413,7 @@
       </c>
       <c r="AG57" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;압력방출장치&lt;/strong&gt;다. 나머지 셋은 &lt;strong&gt;보일러&lt;/strong&gt;의 방호장치다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;압력용기와 보일러의 안전장치&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;압력용기&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보일러&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;장치&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;압력방출장치(안전밸브 · 파열판)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;압력방출장치 · 압력제한스위치 · 고저수위조절장치 · 화염검출기&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;설치 대상&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안지름 150 [mm] 를 넘는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;작동&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최고사용압력 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;2개 이상이면 나머지는 1.05배 이하&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;검사&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;매년 1회 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;압력방출장치&lt;/strong&gt;다. 나머지 셋은 &lt;strong&gt;보일러&lt;/strong&gt;의 방호장치다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;압력용기와 보일러의 안전장치&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;압력용기&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보일러&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;장치&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;압력방출장치(안전밸브 · 파열판)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;압력방출장치 · 압력제한스위치 · 고저수위조절장치 · 화염검출기&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;설치 대상&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안지름 150 [mm]를 넘는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;작동&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최고사용압력 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;2개 이상이면 나머지는 1.05배 이하&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;검사&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;매년 1회 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH57" s="32" t="inlineStr">
@@ -8419,7 +8423,7 @@
       </c>
       <c r="AI57" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;압력용기의 안전장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;압력용기는 물을 끓이지 않으므로 수위도 화염도 없다&lt;/strong&gt; — &lt;strong&gt;남는 것은 압력을 빼는 장치 하나&lt;/strong&gt; 뿐이다. &lt;strong&gt;보일러의 네 장치와 견주어&lt;/strong&gt; 두면 갈린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;압력용기는 압력방출장치&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;압력용기의 안전장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;압력용기는 물을 끓이지 않으므로 수위도 화염도 없다&lt;/strong&gt; — &lt;strong&gt;남는 것은 압력을 빼는 장치 하나&lt;/strong&gt;뿐이다. &lt;strong&gt;보일러의 네 장치와 견주어&lt;/strong&gt; 두면 갈린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;압력용기는 압력방출장치&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8667,12 +8671,12 @@
       </c>
       <c r="AG59" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;10% 이상 벌어지면 폐기&lt;/strong&gt; 한다. &lt;strong&gt;훅이 벌어지면 짐이 빠진다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;레버풀러ㆍ체인블록 사용 시 준수사항&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사항&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;훅의 입구 간격이 제품사양서 기준으로 10% 이상 벌어진 것은 폐기한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정격하중을 초과해 사용하지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;체인이 꼬이거나 뒤틀리거나 비틀리지 않게 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;체인블록은 체인의 꼬임과 헝클어짐이 없도록 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;레버풀러 작업 중 훅이 빠질 우려가 있으면 해지장치를 쓴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;10% 이상 벌어지면 폐기&lt;/strong&gt;한다. &lt;strong&gt;훅이 벌어지면 짐이 빠진다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;레버풀러ㆍ체인블록 사용 시 준수사항&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;사항&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;훅의 입구 간격이 제품사양서 기준으로 10% 이상 벌어진 것은 폐기한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정격하중을 초과해 사용하지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;체인이 꼬이거나 뒤틀리거나 비틀리지 않게 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;체인블록은 체인의 꼬임과 헝클어짐이 없도록 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;레버풀러 작업 중 훅이 빠질 우려가 있으면 해지장치를 쓴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH59" s="32" t="inlineStr">
         <is>
-          <t>① 3% 는 기준값이 아니다.&lt;br&gt;② 5% 도 그렇다.&lt;br&gt;③ 7% 도 그렇다.</t>
+          <t>① 3%는 기준값이 아니다.&lt;br&gt;② 5% 도 그렇다.&lt;br&gt;③ 7% 도 그렇다.</t>
         </is>
       </c>
       <c r="AI59" s="32" t="inlineStr">
@@ -9054,7 +9058,7 @@
       </c>
       <c r="AG62" s="32" t="inlineStr">
         <is>
-          <t>T홈 안길이는 &lt;strong&gt;설치 볼트 지름의 2배 이상&lt;/strong&gt; 이라야 한다. &lt;strong&gt;「이하」가 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;금형 설치·해체의 안전사항&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;설치용구는 프레스의 구조에 맞는 것으로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T홈 안길이는 설치 볼트 지름의 2배 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「이하」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고정볼트는 고정 뒤 나사산 3 ~ 4개 정도만 짧게 남긴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;슬라이드 면과의 협착을 막는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고정용 브래킷은 수평, 고정볼트는 수직으로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전블록을 설치하고 전원을 끈다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>T홈 안길이는 &lt;strong&gt;설치 볼트 지름의 2배 이상&lt;/strong&gt;이라야 한다. &lt;strong&gt;「이하」가 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;금형 설치·해체의 안전사항&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;설치용구는 프레스의 구조에 맞는 것으로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T홈 안길이는 설치 볼트 지름의 2배 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「이하」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고정볼트는 고정 뒤 나사산 3 ~ 4개 정도만 짧게 남긴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;슬라이드 면과의 협착을 막는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고정용 브래킷은 수평, 고정볼트는 수직으로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전블록을 설치하고 전원을 끈다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH62" s="32" t="inlineStr">
@@ -9183,12 +9187,12 @@
       </c>
       <c r="AG63" s="32" t="inlineStr">
         <is>
-          <t>제2종 접지저항은 $\dfrac{150}{10} = 15$ [Ω] 이다. $E = 220 \times \dfrac{30}{15 + 30} \fallingdotseq 146.7$ [V] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;누전 시 외함의 대지전압&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 제2종 접지저항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R_{2} = \dfrac{150}{1 \text{선 지락전류}} = \dfrac{150}{10} = 15$ [Ω]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;여기서 갈린다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 분압&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$E = V \times \dfrac{R_{3}}{R_{2} + R_{3}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③ 값&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;220 × 30/45 = 146.7 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인체저항 10,000 [Ω]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;접지저항보다 훨씬 커 분압에 거의 영향이 없다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>제2종 접지저항은 $\dfrac{150}{10} = 15$ [Ω]이다. $E = 220 \times \dfrac{30}{15 + 30} \fallingdotseq 146.7$ [V]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;누전 시 외함의 대지전압&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 제2종 접지저항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R_{2} = \dfrac{150}{1 \text{선 지락전류}} = \dfrac{150}{10} = 15$ [Ω]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;여기서 갈린다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 분압&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$E = V \times \dfrac{R_{3}}{R_{2} + R_{3}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③ 값&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;220 × 30/45 = 146.7 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인체저항 10,000 [Ω]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;접지저항보다 훨씬 커 분압에 거의 영향이 없다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH63" s="32" t="inlineStr">
         <is>
-          <t>① 165.6 [V] 는 계산과 맞지 않는다.&lt;br&gt;③ 127.5 [V] 도 그렇다.&lt;br&gt;④ 116.7 [V] 도 그렇다.</t>
+          <t>① 165.6 [V]는 계산과 맞지 않는다.&lt;br&gt;③ 127.5 [V] 도 그렇다.&lt;br&gt;④ 116.7 [V] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI63" s="32" t="inlineStr">
@@ -9317,7 +9321,7 @@
       </c>
       <c r="AH64" s="32" t="inlineStr">
         <is>
-          <t>① 0.5 [m] 는 한 걸음으로 보기에 짧다.&lt;br&gt;③ 1.5 [m] 는 기준값이 아니다.&lt;br&gt;④ 2.0 [m] 도 그렇다.</t>
+          <t>① 0.5 [m]는 한 걸음으로 보기에 짧다.&lt;br&gt;③ 1.5 [m]는 기준값이 아니다.&lt;br&gt;④ 2.0 [m] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI64" s="32" t="inlineStr">
@@ -9575,12 +9579,12 @@
       </c>
       <c r="AH66" s="32" t="inlineStr">
         <is>
-          <t>① 50% 는 4분 이내의 소생률이다.&lt;br&gt;② 60% 는 표에 없는 값이다.&lt;br&gt;③ 75% 는 3분 이내의 소생률이다.</t>
+          <t>① 50%는 4분 이내의 소생률이다.&lt;br&gt;② 60%는 표에 없는 값이다.&lt;br&gt;③ 75%는 3분 이내의 소생률이다.</t>
         </is>
       </c>
       <c r="AI66" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;감전자의 소생률&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「1분 95 · 3분 75 · 4분 50 · 5분 25 · 6분 10」&lt;/strong&gt;이라는 다섯 값이다 — &lt;strong&gt;보기에 75 와 50 이 함께 놓여&lt;/strong&gt; 있어 시간을 잘못 보면 그리로 끌린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1분 이내면 95%&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;감전자의 소생률&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「1분 95 · 3분 75 · 4분 50 · 5분 25 · 6분 10」&lt;/strong&gt;이라는 다섯 값이다 — &lt;strong&gt;보기에 75와 50이 함께 놓여&lt;/strong&gt; 있어 시간을 잘못 보면 그리로 끌린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1분 이내면 95%&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9833,7 +9837,7 @@
       </c>
       <c r="AH68" s="32" t="inlineStr">
         <is>
-          <t>① 최소 감지전류는 겨우 느끼는 1 [mA] 다.&lt;br&gt;③ 고통 한계전류는 참을 수 있는 한계인 7 ~ 8 [mA] 다.&lt;br&gt;④ 마비 한계전류는 손을 뗄 수 없는 불수전류다.</t>
+          <t>① 최소 감지전류는 겨우 느끼는 1 [mA]다.&lt;br&gt;③ 고통 한계전류는 참을 수 있는 한계인 7 ~ 8 [mA]다.&lt;br&gt;④ 마비 한계전류는 손을 뗄 수 없는 불수전류다.</t>
         </is>
       </c>
       <c r="AI68" s="32" t="inlineStr">
@@ -9958,12 +9962,12 @@
       </c>
       <c r="AH69" s="32" t="inlineStr">
         <is>
-          <t>① 6,000 [cm³] 와 0.4 [mm] 는 값이 맞지 않는다.&lt;br&gt;② 1,800 [cm³] 와 0.6 [mm] 도 그렇다.&lt;br&gt;③ 4,500 [cm³] 와 8 [mm] 도 그렇다.</t>
+          <t>① 6,000 [cm³]와 0.4 [mm]는 값이 맞지 않는다.&lt;br&gt;② 1,800 [cm³]와 0.6 [mm] 도 그렇다.&lt;br&gt;③ 4,500 [cm³]와 8 [mm] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI69" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;화염일주한계와 폭발등급&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;보기의 0.4 와 0.6 은 폭발등급의 경계값&lt;/strong&gt;이라 눈에 익어 끌린다 — &lt;strong&gt;여기서 묻는 것은 「용기의 치수」&lt;/strong&gt;이지 등급의 경계가 아니다. &lt;strong&gt;8,000 [cm³] 와 25 [mm]&lt;/strong&gt;라는 짝을 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;내용적 8,000 [cm³], 안길이 25 [mm]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;화염일주한계와 폭발등급&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;보기의 0.4와 0.6은 폭발등급의 경계값&lt;/strong&gt;이라 눈에 익어 끌린다 — &lt;strong&gt;여기서 묻는 것은 「용기의 치수」&lt;/strong&gt;이지 등급의 경계가 아니다. &lt;strong&gt;8,000 [cm³]와 25 [mm]&lt;/strong&gt;라는 짝을 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;내용적 8,000 [cm³], 안길이 25 [mm]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10079,12 +10083,12 @@
       </c>
       <c r="AH70" s="32" t="inlineStr">
         <is>
-          <t>① 4 [mA] 는 지나치게 작다.&lt;br&gt;③ 400 [mA] 는 지나치게 크다.&lt;br&gt;④ 800 [mA] 도 그렇다.</t>
+          <t>① 4 [mA]는 지나치게 작다.&lt;br&gt;③ 400 [mA]는 지나치게 크다.&lt;br&gt;④ 800 [mA] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI70" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;과도전류의 허용한계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「오래 흐를수록 견딜 수 있는 전류가 작아진다」&lt;/strong&gt;는 방향은 심실세동전류 $I = 165 / \sqrt{T}$ 와 같다. &lt;strong&gt;보기가 10배씩 벌어져 있어 자릿수만 맞춰도&lt;/strong&gt; 좁혀진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;파두장 700 [μs] 는 40 [mA]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;과도전류의 허용한계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「오래 흐를수록 견딜 수 있는 전류가 작아진다」&lt;/strong&gt;는 방향은 심실세동전류 $I = 165 / \sqrt{T}$와 같다. &lt;strong&gt;보기가 10배씩 벌어져 있어 자릿수만 맞춰도&lt;/strong&gt; 좁혀진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;파두장 700 [μs]는 40 [mA]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10203,12 +10207,12 @@
       </c>
       <c r="AG71" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;IP66&lt;/strong&gt;이다. &lt;strong&gt;기름이 새거나 물이 들어가면 방폭이 무너지기&lt;/strong&gt; 때문이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;IP 등급의 읽는 법&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;자리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;첫째 자리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고체(먼지)를 얼마나 막나&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6 = 완전 방진&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;둘째 자리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;물을 얼마나 막나&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6 = 강한 물줄기에도 견딤&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;IP66&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;먼지가 전혀 들어가지 않고 강한 물줄기에도 견딘다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;유입방폭구조 o 의 최소 등급&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;IP66&lt;/strong&gt;이다. &lt;strong&gt;기름이 새거나 물이 들어가면 방폭이 무너지기&lt;/strong&gt; 때문이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;IP 등급의 읽는 법&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;자리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;뜻&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;첫째 자리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고체(먼지)를 얼마나 막나&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6 = 완전 방진&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;둘째 자리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;물을 얼마나 막나&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6 = 강한 물줄기에도 견딤&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;IP66&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;먼지가 전혀 들어가지 않고 강한 물줄기에도 견딘다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;유입방폭구조 o의 최소 등급&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH71" s="32" t="inlineStr">
         <is>
-          <t>① IP44 는 기준에 못 미친다.&lt;br&gt;② IP54 도 그렇다.&lt;br&gt;③ IP55 도 그렇다.</t>
+          <t>① IP44는 기준에 못 미친다.&lt;br&gt;② IP54 도 그렇다.&lt;br&gt;③ IP55 도 그렇다.</t>
         </is>
       </c>
       <c r="AI71" s="32" t="inlineStr">
@@ -10471,7 +10475,7 @@
       </c>
       <c r="AI73" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;폭발위험장소의 설정&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;폭발은 「공기와 고루 섞인 기체나 가루」&lt;/strong&gt; 라야 일어난다 — &lt;strong&gt;종이 뭉치는 타기는 해도 공기와 섞이지 않아 폭발하지 않는다&lt;/strong&gt;. &lt;strong&gt;다만 그 가루(분진)라면 이야기가 다르다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;덩어리진 가연물은 화재위험장소&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;폭발위험장소의 설정&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;폭발은 「공기와 고루 섞인 기체나 가루」&lt;/strong&gt;라야 일어난다 — &lt;strong&gt;종이 뭉치는 타기는 해도 공기와 섞이지 않아 폭발하지 않는다&lt;/strong&gt;. &lt;strong&gt;다만 그 가루(분진)라면 이야기가 다르다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;덩어리진 가연물은 화재위험장소&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10604,7 @@
       </c>
       <c r="AI74" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;주수의 형태&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「물이 끊겨 있느냐」&lt;/strong&gt;가 갈림선이다 — &lt;strong&gt;물방울로 흩어지면 전기가 이어 흐르지 못한다&lt;/strong&gt;. &lt;strong&gt;봉상만 이어져 있어 감전&lt;/strong&gt; 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;봉상주수는 전기화재에 못 쓴다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;주수의 형태&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「물이 끊겨 있느냐」&lt;/strong&gt;가 갈림선이다 — &lt;strong&gt;물방울로 흩어지면 전기가 이어 흐르지 못한다&lt;/strong&gt;. &lt;strong&gt;봉상만 이어져 있어 감전&lt;/strong&gt;된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;봉상주수는 전기화재에 못 쓴다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10723,17 +10727,17 @@
       </c>
       <c r="AG75" s="32" t="inlineStr">
         <is>
-          <t>인체와 $R_{3}$ 이 병렬이므로 $\dfrac{80 \times 3 {,} 000}{3 {,} 080} = 77.9$ [Ω] 이다. 지락전류는 $\dfrac{220}{20 + 77.9} = 2.25$ [A], 외함전압은 $2.25 \times 77.9 = 175$ [V] 이므로 인체전류는 $\dfrac{175}{3 {,} 000} \fallingdotseq 58$ [mA] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;인체통과전류의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 병렬저항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{80 \times 3 {,} 000}{80 + 3 {,} 000} = 77.9$ [Ω]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인체는 &lt;/u&gt;$R_{3}$&lt;u&gt; 과 병렬&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 지락전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;220 ÷ (20 + 77.9) = 2.25 [A]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③ 외함전압&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.25 × 77.9 = 175 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;④ 인체전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;175 ÷ 3,000 = 58 [mA]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>인체와 $R_{3}$이 병렬이므로 $\dfrac{80 \times 3 {,} 000}{3 {,} 080} = 77.9$ [Ω]이다. 지락전류는 $\dfrac{220}{20 + 77.9} = 2.25$ [A], 외함전압은 $2.25 \times 77.9 = 175$ [V]이므로 인체전류는 $\dfrac{175}{3 {,} 000} \fallingdotseq 58$ [mA]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;인체통과전류의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 병렬저항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{80 \times 3 {,} 000}{80 + 3 {,} 000} = 77.9$ [Ω]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;인체는 &lt;/u&gt;$R_{3}$&lt;u&gt;과 병렬&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 지락전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;220 ÷ (20 + 77.9) = 2.25 [A]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③ 외함전압&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.25 × 77.9 = 175 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;④ 인체전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;175 ÷ 3,000 = 58 [mA]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH75" s="32" t="inlineStr">
         <is>
-          <t>① 35 [mA] 는 계산과 맞지 않는다.&lt;br&gt;② 47 [mA] 도 그렇다.&lt;br&gt;④ 66 [mA] 는 병렬을 셈하지 않은 값에 가깝다.</t>
+          <t>① 35 [mA]는 계산과 맞지 않는다.&lt;br&gt;② 47 [mA] 도 그렇다.&lt;br&gt;④ 66 [mA]는 병렬을 셈하지 않은 값에 가깝다.</t>
         </is>
       </c>
       <c r="AI75" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;누전 시 인체통과전류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;사람이 외함을 잡으면 인체가 &lt;/strong&gt;$R_{3}$&lt;strong&gt; 과 나란히&lt;/strong&gt; 놓인다 — &lt;strong&gt;병렬로 묶어 낮아진 저항&lt;/strong&gt;을 먼저 구해야 한다. &lt;strong&gt;인체저항이 훨씬 커서 대부분의 전류는 &lt;/strong&gt;$R_{3}$&lt;strong&gt; 으로 빠진다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;인체는 외함 접지저항과 병렬&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;누전 시 인체통과전류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;사람이 외함을 잡으면 인체가 &lt;/strong&gt;$R_{3}$&lt;strong&gt;과 나란히&lt;/strong&gt; 놓인다 — &lt;strong&gt;병렬로 묶어 낮아진 저항&lt;/strong&gt;을 먼저 구해야 한다. &lt;strong&gt;인체저항이 훨씬 커서 대부분의 전류는 &lt;/strong&gt;$R_{3}$&lt;strong&gt;으로 빠진다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;인체는 외함 접지저항과 병렬&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10861,12 @@
       </c>
       <c r="AH76" s="32" t="inlineStr">
         <is>
-          <t>① 0.1 [MΩ] 은 옛 기준의 대지전압 150 [V] 이하 값이다.&lt;br&gt;② 0.2 [MΩ] 은 옛 기준의 150 [V] 초과 300 [V] 이하 값이다.&lt;br&gt;④ 0.4 [MΩ] 은 400 [V] 이상의 값이다.</t>
+          <t>① 0.1 [MΩ]은 옛 기준의 대지전압 150 [V] 이하 값이다.&lt;br&gt;② 0.2 [MΩ]은 옛 기준의 150 [V] 초과 300 [V] 이하 값이다.&lt;br&gt;④ 0.4 [MΩ]은 400 [V] 이상의 값이다.</t>
         </is>
       </c>
       <c r="AI76" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;저압전로의 절연저항&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;옛 기준은 「0.1 · 0.2 · 0.3 · 0.4」 네 칸&lt;/strong&gt; 이었고 &lt;strong&gt;380 [V] 는 400 [V] 미만이라 0.3&lt;/strong&gt;이다. &lt;strong&gt;KEC 는 이를 세 줄로 줄이고 값도 올렸다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;옛 기준 400 [V] 미만은 0.3 [MΩ]&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;KEC 시행(2021.1.1)&lt;/u&gt;으로 저압전로의 절연저항은 &lt;u&gt;SELV·PELV 0.5 [MΩ], FELV 및 500 [V] 이하 1.0 [MΩ], 500 [V] 초과 1.0 [MΩ]&lt;/u&gt; 세 줄로 바뀌었다. 여기 실린 0.3 [MΩ] 은 옛 기준이다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;저압전로의 절연저항&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;옛 기준은 「0.1 · 0.2 · 0.3 · 0.4」 네 칸&lt;/strong&gt; 이었고 &lt;strong&gt;380 [V]는 400 [V] 미만이라 0.3&lt;/strong&gt;이다. &lt;strong&gt;KEC는 이를 세 줄로 줄이고 값도 올렸다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;옛 기준 400 [V] 미만은 0.3 [MΩ]&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; &lt;u&gt;KEC 시행(2021.1.1)&lt;/u&gt;으로 저압전로의 절연저항은 &lt;u&gt;SELV·PELV 0.5 [MΩ], FELV 및 500 [V] 이하 1.0 [MΩ], 500 [V] 초과 1.0 [MΩ]&lt;/u&gt; 세 줄로 바뀌었다. 여기 실린 0.3 [MΩ]은 옛 기준이다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10981,17 +10985,17 @@
       </c>
       <c r="AG77" s="32" t="inlineStr">
         <is>
-          <t>전동기 정격전류의 합은 45 [A], 그 밖의 부하는 60 [A] 다. 간선의 허용전류는 $45 \times 1.1 + 60 = 109.5$ [A] 이므로 차단기는 $45 \times 3 + 60 = 195$ [A] 이하이면서 허용전류의 2.5배 이하 — &lt;strong&gt;보기 가운데 200 [A]&lt;/strong&gt;이 답이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;전동기 간선의 과전류차단기&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전동기 정격전류의 합&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;20 + 25 = 45 [A]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;그 밖의 부하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 × 6 = 60 [A]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;간선의 허용전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;45 × 1.1 + 60 = 109.5 [A]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;합이 50 [A] 이하이면 1.25배&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;차단기의 정격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전동기 합 × 3 + 그 밖의 부하 = 195 [A]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;허용전류의 2.5배와 견주어 작은 쪽&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>전동기 정격전류의 합은 45 [A], 그 밖의 부하는 60 [A]다. 간선의 허용전류는 $45 \times 1.1 + 60 = 109.5$ [A]이므로 차단기는 $45 \times 3 + 60 = 195$ [A] 이하이면서 허용전류의 2.5배 이하 — &lt;strong&gt;보기 가운데 200 [A]&lt;/strong&gt;이 답이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;전동기 간선의 과전류차단기&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전동기 정격전류의 합&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;20 + 25 = 45 [A]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;그 밖의 부하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 × 6 = 60 [A]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;간선의 허용전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;45 × 1.1 + 60 = 109.5 [A]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;합이 50 [A] 이하이면 1.25배&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;차단기의 정격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전동기 합 × 3 + 그 밖의 부하 = 195 [A]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;허용전류의 2.5배와 견주어 작은 쪽&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH77" s="32" t="inlineStr">
         <is>
-          <t>② 150 [A] 는 답으로 제시된 값이 아니다.&lt;br&gt;③ 125 [A] 도 그렇다.&lt;br&gt;④ 100 [A] 는 간선 허용전류에도 못 미친다.</t>
+          <t>② 150 [A]는 답으로 제시된 값이 아니다.&lt;br&gt;③ 125 [A] 도 그렇다.&lt;br&gt;④ 100 [A]는 간선 허용전류에도 못 미친다.</t>
         </is>
       </c>
       <c r="AI77" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;전동기 간선의 과전류차단기&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;전동기는 기동할 때 정격의 몇 배가 흐르므로 차단기를 넉넉히&lt;/strong&gt; 잡는다 — &lt;strong&gt;「전동기 정격의 3배 + 그 밖의 부하」&lt;/strong&gt;와 &lt;strong&gt;「간선 허용전류의 2.5배」&lt;/strong&gt; 가운데 작은 쪽으로 정한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전동기 합 × 3 + 그 밖의 부하&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 간선의 허용전류와 과전류차단기 산정은 &lt;u&gt;KEC 로 옮겨지며 조문과 계수가 정리&lt;/u&gt; 되었다. 여기 실린 것은 옛 판단기준에 따른 것이므로 현행 KEC 의 해당 조문을 함께 확인해 둘 것.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;전동기 간선의 과전류차단기&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;전동기는 기동할 때 정격의 몇 배가 흐르므로 차단기를 넉넉히&lt;/strong&gt; 잡는다 — &lt;strong&gt;「전동기 정격의 3배 + 그 밖의 부하」&lt;/strong&gt;와 &lt;strong&gt;「간선 허용전류의 2.5배」&lt;/strong&gt; 가운데 작은 쪽으로 정한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;전동기 합 × 3 + 그 밖의 부하&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 간선의 허용전류와 과전류차단기 산정은 &lt;u&gt;KEC로 옮겨지며 조문과 계수가 정리&lt;/u&gt; 되었다. 여기 실린 것은 옛 판단기준에 따른 것이므로 현행 KEC의 해당 조문을 함께 확인해 둘 것.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11110,7 +11114,7 @@
       </c>
       <c r="AG78" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;저압 수용장소&lt;/strong&gt;는 피뢰기 설치대상이 아니다. &lt;strong&gt;특고압에서 공급받는 수용장소&lt;/strong&gt; 라야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;피뢰기를 설치해야 하는 곳&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장소&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발전소·변전소의 가공전선 인입구와 인출구&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가공전선로에 접속하는 배전용 변압기의 고압측과 특고압측&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;특고압 가공전선로에서 공급받는 수용장소의 인입구&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가공전선로와 지중전선로가 접속하는 곳&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;저압 수용장소의 인입구&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설치대상이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;저압 수용장소&lt;/strong&gt;는 피뢰기 설치대상이 아니다. &lt;strong&gt;특고압에서 공급받는 수용장소&lt;/strong&gt;라야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;피뢰기를 설치해야 하는 곳&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장소&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발전소·변전소의 가공전선 인입구와 인출구&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가공전선로에 접속하는 배전용 변압기의 고압측과 특고압측&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;특고압 가공전선로에서 공급받는 수용장소의 인입구&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가공전선로와 지중전선로가 접속하는 곳&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;저압 수용장소의 인입구&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설치대상이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH78" s="32" t="inlineStr">
@@ -11239,7 +11243,7 @@
       </c>
       <c r="AG79" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;흙 자체는 전기가 잘 통하지 않는다&lt;/strong&gt;. &lt;strong&gt;단면적이 사실상 무한히 넓어&lt;/strong&gt; 전체 저항이 작아지는 것이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;대지를 접지로 쓰는 까닭&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대지는 넓어 전류가 지날 길이 무수히 많다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R = \rho \dfrac{l}{A}$ 에서 &lt;u&gt;A 가 무한대&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;그래서 전체 저항이 작다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;흙의 성분(규소·알루미나·철분)은 까닭이 아니다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;흙 자체는 저항이 크다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;접지저항의 대부분&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전극 바로 둘레의 좁은 곳에서 생긴다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;흙 자체는 전기가 잘 통하지 않는다&lt;/strong&gt;. &lt;strong&gt;단면적이 사실상 무한히 넓어&lt;/strong&gt; 전체 저항이 작아지는 것이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;대지를 접지로 쓰는 까닭&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;대지는 넓어 전류가 지날 길이 무수히 많다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R = \rho \dfrac{l}{A}$에서 &lt;u&gt;A가 무한대&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;그래서 전체 저항이 작다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;흙의 성분(규소·알루미나·철분)은 까닭이 아니다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;흙 자체는 저항이 크다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;접지저항의 대부분&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;전극 바로 둘레의 좁은 곳에서 생긴다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH79" s="32" t="inlineStr">
@@ -11249,7 +11253,7 @@
       </c>
       <c r="AI79" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;접지의 원리&lt;/strong&gt;&lt;br&gt;$R = \rho \dfrac{l}{A}$ 에서 &lt;strong&gt;대지는 A 가 사실상 무한대&lt;/strong&gt;라 &lt;strong&gt;저항률이 커도 전체 저항이 작아진다&lt;/strong&gt;. &lt;strong&gt;성분을 드는 보기 셋은 모두 걸러진다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;넓어서 저항이 작다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;접지의 원리&lt;/strong&gt;&lt;br&gt;$R = \rho \dfrac{l}{A}$에서 &lt;strong&gt;대지는 A가 사실상 무한대&lt;/strong&gt;라 &lt;strong&gt;저항률이 커도 전체 저항이 작아진다&lt;/strong&gt;. &lt;strong&gt;성분을 드는 보기 셋은 모두 걸러진다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;넓어서 저항이 작다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11626,12 +11630,12 @@
       </c>
       <c r="AG82" s="32" t="inlineStr">
         <is>
-          <t>방사선식은 &lt;strong&gt;방사선 장해와 취급에 각별히 주의&lt;/strong&gt; 해야 한다. &lt;strong&gt;「주의를 요하지 않아도 된다」가 뒤집혀&lt;/strong&gt; 있다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;제전기의 종류와 특징&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;특징&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전압인가식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;방전침에 약 7,000 [V] 를 걸어 코로나 방전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;제전능력이 가장 크다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;자기방전식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대전체 자신의 전계로 방전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;2 [kV] 안팎의 대전이 남는다 · 필름 권취·셀로판·섬유공장&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;방사선식(이온식)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;방사선의 전리작용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;제전효율이 낮으나 폭발위험지역에 알맞다&lt;/u&gt; · &lt;u&gt;방사선 장해에 각별히 주의&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이동물체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;방사선식이 알맞다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>방사선식은 &lt;strong&gt;방사선 장해와 취급에 각별히 주의&lt;/strong&gt;해야 한다. &lt;strong&gt;「주의를 요하지 않아도 된다」가 뒤집혀&lt;/strong&gt; 있다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;제전기의 종류와 특징&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;특징&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전압인가식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;방전침에 약 7,000 [V]를 걸어 코로나 방전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;제전능력이 가장 크다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;자기방전식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대전체 자신의 전계로 방전&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;2 [kV] 안팎의 대전이 남는다 · 필름 권취·셀로판·섬유공장&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;방사선식(이온식)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;방사선의 전리작용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;제전효율이 낮으나 폭발위험지역에 알맞다&lt;/u&gt; · &lt;u&gt;방사선 장해에 각별히 주의&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이동물체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;방사선식이 알맞다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH82" s="32" t="inlineStr">
         <is>
-          <t>① 전압인가식이 약 7,000 [V] 를 걸어 이온을 만드는 것은 맞다.&lt;br&gt;③ 이온식(방사선식)이 제전효율은 낮으나 폭발위험지역에 알맞은 것도 맞다.&lt;br&gt;④ 자기방전식에 2 [kV] 안팎의 대전이 남는 것도 맞다.</t>
+          <t>① 전압인가식이 약 7,000 [V]를 걸어 이온을 만드는 것은 맞다.&lt;br&gt;③ 이온식(방사선식)이 제전효율은 낮으나 폭발위험지역에 알맞은 것도 맞다.&lt;br&gt;④ 자기방전식에 2 [kV] 안팎의 대전이 남는 것도 맞다.</t>
         </is>
       </c>
       <c r="AI82" s="32" t="inlineStr">
@@ -11997,17 +12001,17 @@
       </c>
       <c r="AG85" s="32" t="inlineStr">
         <is>
-          <t>부탄은 $O_{2} = 6.5$ 이므로 $C_{\mathrm{st}} = \dfrac{100}{1 + 4.77 \times 6.5} = 3.13$ 이다. $L = 0.55 \times 3.13 \fallingdotseq 1.7$ [vol%] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;존스(Jones) 식&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 산소 몰수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;부탄은 6.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$C_{4} H_{10} + 6.5 O_{2} \rightarrow 4 CO_{2} + 5 H_{2} O$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 화학양론농도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$C_{\mathrm{st}} = \dfrac{100}{1 + 4.77 \times 6.5} = 3.13$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;4.77 = 100/21&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③ 폭발하한계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.55 × 3.13 = 1.7 [vol%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭발상한계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3.50 × 3.13 = 10.9 [vol%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>부탄은 $O_{2} = 6.5$이므로 $C_{\mathrm{st}} = \dfrac{100}{1 + 4.77 \times 6.5} = 3.13$이다. $L = 0.55 \times 3.13 \fallingdotseq 1.7$ [vol%]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;존스(Jones) 식&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 산소 몰수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;부탄은 6.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$C_{4} H_{10} + 6.5 O_{2} \rightarrow 4 CO_{2} + 5 H_{2} O$&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 화학양론농도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$C_{\mathrm{st}} = \dfrac{100}{1 + 4.77 \times 6.5} = 3.13$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;4.77 = 100/21&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③ 폭발하한계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.55 × 3.13 = 1.7 [vol%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭발상한계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3.50 × 3.13 = 10.9 [vol%]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH85" s="32" t="inlineStr">
         <is>
-          <t>① 1.4 [vol%] 는 계산과 맞지 않는다.&lt;br&gt;③ 2.0 [vol%] 도 그렇다.&lt;br&gt;④ 2.3 [vol%] 도 그렇다.</t>
+          <t>① 1.4 [vol%]는 계산과 맞지 않는다.&lt;br&gt;③ 2.0 [vol%] 도 그렇다.&lt;br&gt;④ 2.3 [vol%] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI85" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;존스 식&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;4.77 은 「100 ÷ 21」&lt;/strong&gt; — &lt;strong&gt;공기에서 산소를 1 몰 얻으려면 공기 4.77 몰이 필요&lt;/strong&gt; 하다는 뜻이다. &lt;strong&gt;하한 0.55, 상한 3.50 이라는 계수&lt;/strong&gt;를 함께 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $C_{\mathrm{st}} = 100 / ( 1 + 4.77 O_{2} )$, $L = 0.55 C_{\mathrm{st}}$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;존스 식&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;4.77은 「100 ÷ 21」&lt;/strong&gt; — &lt;strong&gt;공기에서 산소를 1 몰 얻으려면 공기 4.77 몰이 필요&lt;/strong&gt; 하다는 뜻이다. &lt;strong&gt;하한 0.55, 상한 3.50이라는 계수&lt;/strong&gt;를 함께 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $C_{\mathrm{st}} = 100 / ( 1 + 4.77 O_{2} )$, $L = 0.55 C_{\mathrm{st}}$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12126,7 +12130,7 @@
       </c>
       <c r="AG86" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;니트로셀룰로오스는 알코올에 적셔 보관&lt;/strong&gt; 한다. &lt;strong&gt;오히려 안전해지는 짝&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;혼합·접촉의 위험&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;짝&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;위험&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;니트로셀룰로오스 + 알코올&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;낮다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;적셔 두면 마찰·충격에 안정&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;나트륨 + 알코올&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;알코올과 반응해 수소 발생&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;염소산칼륨(산화성) + 유황(가연성)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;산소를 주는 쪽 + 받는 쪽&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;황화인(가연성) + 무기과산화물(산화성)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;같은 짝&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;니트로셀룰로오스는 알코올에 적셔 보관&lt;/strong&gt;한다. &lt;strong&gt;오히려 안전해지는 짝&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;혼합·접촉의 위험&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;짝&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;위험&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;니트로셀룰로오스 + 알코올&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;낮다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;적셔 두면 마찰·충격에 안정&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;나트륨 + 알코올&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;알코올과 반응해 수소 발생&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;염소산칼륨(산화성) + 유황(가연성)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;산소를 주는 쪽 + 받는 쪽&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;황화인(가연성) + 무기과산화물(산화성)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;같은 짝&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH86" s="32" t="inlineStr">
@@ -12265,7 +12269,7 @@
       </c>
       <c r="AI87" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;불활성화(퍼지)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;불활성기체는 「타지 않고 · 반응하지 않고 · 그대로 남아 있어야」&lt;/strong&gt; 한다 — &lt;strong&gt;수증기는 식으면 물이 되어 빠져나가므로 산소농도를 계속 눌러 둘 수&lt;/strong&gt; 없다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;수증기는 응축해 사라진다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;불활성화(퍼지)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;불활성기체는 「타지 않고 · 반응하지 않고 · 그대로 남아 있어야」&lt;/strong&gt;한다 — &lt;strong&gt;수증기는 식으면 물이 되어 빠져나가므로 산소농도를 계속 눌러 둘 수&lt;/strong&gt; 없다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;수증기는 응축해 사라진다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12775,17 +12779,17 @@
       </c>
       <c r="AG91" s="32" t="inlineStr">
         <is>
-          <t>$R = \dfrac{10 {,} 000}{20 {,} 000} + \dfrac{20 {,} 000}{50 {,} 000} = 0.5 + 0.4 = 0.9$ 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;R 값의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R 값&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R = \sum \dfrac{\text{취급량}_{i}}{\text{규정수량}_{i}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;염소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10,000 ÷ 20,000 = 0.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;20,000 ÷ 50,000 = 0.4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;합&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.9&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;R ≥ 1 이면 제출대상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;판정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.9 &amp;lt; 1 이므로 제출대상이 아니다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$R = \dfrac{10 {,} 000}{20 {,} 000} + \dfrac{20 {,} 000}{50 {,} 000} = 0.5 + 0.4 = 0.9$다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;R 값의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R 값&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R = \sum \dfrac{\text{취급량}_{i}}{\text{규정수량}_{i}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;염소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10,000 ÷ 20,000 = 0.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;20,000 ÷ 50,000 = 0.4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;합&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.9&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;R ≥ 1 이면 제출대상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;판정&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.9 &amp;lt; 1이므로 제출대상이 아니다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH91" s="32" t="inlineStr">
         <is>
-          <t>② 1.2 는 계산과 맞지 않는다.&lt;br&gt;③ 1.5 도 그렇다.&lt;br&gt;④ 1.8 도 그렇다.</t>
+          <t>② 1.2는 계산과 맞지 않는다.&lt;br&gt;③ 1.5 도 그렇다.&lt;br&gt;④ 1.8 도 그렇다.</t>
         </is>
       </c>
       <c r="AI91" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;공정안전보고서의 제출대상&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;여러 물질을 다룰 때에는 「각각의 비를 더해 1 이 넘는가」&lt;/strong&gt;를 본다 — &lt;strong&gt;노출지수(EI)와 똑같은 꼴&lt;/strong&gt;이다. &lt;strong&gt;0.9 라면 아슬아슬하게 대상이 아니다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $R = \sum \text{취급량} / \text{규정수량}$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;공정안전보고서의 제출대상&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;여러 물질을 다룰 때에는 「각각의 비를 더해 1이 넘는가」&lt;/strong&gt;를 본다 — &lt;strong&gt;노출지수(EI)와 똑같은 꼴&lt;/strong&gt;이다. &lt;strong&gt;0.9 라면 아슬아슬하게 대상이 아니다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $R = \sum \text{취급량} / \text{규정수량}$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13042,7 +13046,7 @@
       </c>
       <c r="AH93" s="32" t="inlineStr">
         <is>
-          <t>① 경구 1,000 · 경피 300 은 두 값을 뒤바꾼 것이다.&lt;br&gt;② 둘 다 1,000 도 아니다.&lt;br&gt;③ 둘 다 300 도 아니다.</t>
+          <t>① 경구 1,000 · 경피 300은 두 값을 뒤바꾼 것이다.&lt;br&gt;② 둘 다 1,000 도 아니다.&lt;br&gt;③ 둘 다 300 도 아니다.</t>
         </is>
       </c>
       <c r="AI93" s="32" t="inlineStr">
@@ -13171,7 +13175,7 @@
       </c>
       <c r="AH94" s="32" t="inlineStr">
         <is>
-          <t>② 암모니아는 25 [ppm] 이다.&lt;br&gt;③ 에탄올은 1,000 [ppm] 으로 가장 높다.&lt;br&gt;④ 메탄올은 200 [ppm] 이다.</t>
+          <t>② 암모니아는 25 [ppm]이다.&lt;br&gt;③ 에탄올은 1,000 [ppm]으로 가장 높다.&lt;br&gt;④ 메탄올은 200 [ppm]이다.</t>
         </is>
       </c>
       <c r="AI94" s="32" t="inlineStr">
@@ -13558,7 +13562,7 @@
       </c>
       <c r="AH97" s="32" t="inlineStr">
         <is>
-          <t>② 10 [m³] 는 기준값이 아니다.&lt;br&gt;③ 100 [m³] 도 그렇다.&lt;br&gt;④ 1,000 [m³] 도 그렇다.</t>
+          <t>② 10 [m³]는 기준값이 아니다.&lt;br&gt;③ 100 [m³] 도 그렇다.&lt;br&gt;④ 1,000 [m³] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI97" s="32" t="inlineStr">
@@ -13687,12 +13691,12 @@
       </c>
       <c r="AH98" s="32" t="inlineStr">
         <is>
-          <t>① 백드래프트는 산소가 모자란 실내에 공기가 들어와 폭발적으로 타는 현상이다.&lt;br&gt;③ 플래시오버는 실내 가연물이 한꺼번에 발화하는 현상이다.&lt;br&gt;④ UVCE 는 새어 나온 증기구름이 퍼졌다 점화되는 폭발이다.</t>
+          <t>① 백드래프트는 산소가 모자란 실내에 공기가 들어와 폭발적으로 타는 현상이다.&lt;br&gt;③ 플래시오버는 실내 가연물이 한꺼번에 발화하는 현상이다.&lt;br&gt;④ UVCE는 새어 나온 증기구름이 퍼졌다 점화되는 폭발이다.</t>
         </is>
       </c>
       <c r="AI98" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;BLEVE&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;BLEVE 는 「탱크 안」, UVCE 는 「탱크 밖」&lt;/strong&gt;이다 — &lt;strong&gt;안에서 끓다 터지면 BLEVE, 새어 나와 퍼졌다 터지면 UVCE&lt;/strong&gt;. &lt;strong&gt;백드래프트와 플래시오버는 실내 화재&lt;/strong&gt;의 이야기다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;탱크가 끓다 터지면 BLEVE&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;BLEVE&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;BLEVE는 「탱크 안」, UVCE는 「탱크 밖」&lt;/strong&gt;이다 — &lt;strong&gt;안에서 끓다 터지면 BLEVE, 새어 나와 퍼졌다 터지면 UVCE&lt;/strong&gt;. &lt;strong&gt;백드래프트와 플래시오버는 실내 화재&lt;/strong&gt;의 이야기다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;탱크가 끓다 터지면 BLEVE&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13811,12 +13815,12 @@
       </c>
       <c r="AG99" s="32" t="inlineStr">
         <is>
-          <t>액체연료는 &lt;strong&gt;시간당 10 [kg] 이상&lt;/strong&gt; 이라야 한다. &lt;strong&gt;5 [kg/h] 는 기준에 못 미친다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;보기별 판정&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;판정&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내용적 2 [m³]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [m³] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;대상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;액체연료 5 [kg/h]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [kg/h] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대상이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기체연료 2 [m³/h]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [m³/h] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;대상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전기 20 [kW]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [kW] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;대상&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>액체연료는 &lt;strong&gt;시간당 10 [kg] 이상&lt;/strong&gt;이라야 한다. &lt;strong&gt;5 [kg/h]는 기준에 못 미친다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;보기별 판정&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;판정&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내용적 2 [m³]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [m³] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;대상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;액체연료 5 [kg/h]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [kg/h] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대상이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기체연료 2 [m³/h]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [m³/h] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;대상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전기 20 [kW]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [kW] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;대상&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH99" s="32" t="inlineStr">
         <is>
-          <t>① 내용적 2 [m³] 는 기준 1 [m³] 를 넘어 대상이다.&lt;br&gt;③ 기체연료 2 [m³/h] 도 기준 1 [m³/h] 를 넘어 대상이다.&lt;br&gt;④ 전기 20 [kW] 도 기준 10 [kW] 를 넘어 대상이다.</t>
+          <t>① 내용적 2 [m³]는 기준 1 [m³]를 넘어 대상이다.&lt;br&gt;③ 기체연료 2 [m³/h] 도 기준 1 [m³/h]를 넘어 대상이다.&lt;br&gt;④ 전기 20 [kW] 도 기준 10 [kW]를 넘어 대상이다.</t>
         </is>
       </c>
       <c r="AI99" s="32" t="inlineStr">
@@ -14452,17 +14456,17 @@
       </c>
       <c r="AG104" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;매 [m²] 당 500 [kg] 이상&lt;/strong&gt;의 하중에 견뎌야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;계단의 설치기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;매 [m²] 당 500 [kg] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전율 4 이상&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계단참&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 3 [m] 를 넘으면 3 [m] 이내마다 너비 1.2 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 1 [m] 이상이면 개방된 쪽에&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;유효높이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 [m] 이내에 장애물이 없을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;매 [m²] 당 500 [kg] 이상&lt;/strong&gt;의 하중에 견뎌야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;계단의 설치기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;매 [m²] 당 500 [kg] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전율 4 이상&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;폭&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계단참&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 3 [m]를 넘으면 3 [m] 이내마다 너비 1.2 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 1 [m] 이상이면 개방된 쪽에&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;유효높이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 [m] 이내에 장애물이 없을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH104" s="32" t="inlineStr">
         <is>
-          <t>① 200 [kg/m²] 는 기준에 못 미친다.&lt;br&gt;② 300 [kg/m²] 도 그렇다.&lt;br&gt;③ 400 [kg/m²] 도 그렇다.</t>
+          <t>① 200 [kg/m²]는 기준에 못 미친다.&lt;br&gt;② 300 [kg/m²] 도 그렇다.&lt;br&gt;③ 400 [kg/m²] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI104" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;계단의 강도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「500 · 4 · 1 · 3-1.2 · 2」&lt;/strong&gt; 다섯 숫자다 — &lt;strong&gt;500 [kg/m²] 는 1 [m²] 에 어른 예닐곱 명이 서는 무게&lt;/strong&gt; 쯤이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;매 [m²] 당 500 [kg] 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;계단의 강도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「500 · 4 · 1 · 3-1.2 · 2」&lt;/strong&gt; 다섯 숫자다 — &lt;strong&gt;500 [kg/m²]는 1 [m²]에 어른 예닐곱 명이 서는 무게&lt;/strong&gt; 쯤이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;매 [m²] 당 500 [kg] 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14973,7 +14977,7 @@
       </c>
       <c r="AH108" s="32" t="inlineStr">
         <is>
-          <t>① 최대제한속도가 시속 10 [km] 를 넘으면 제한속도를 정해 지키게 하는 것은 맞다.&lt;br&gt;③ 화물을 적재할 때 하중이 치우치지 않게 하는 것도 맞다.&lt;br&gt;④ 승차석이 아닌 위치에 사람을 태우지 않는 것도 맞다.</t>
+          <t>① 최대제한속도가 시속 10 [km]를 넘으면 제한속도를 정해 지키게 하는 것은 맞다.&lt;br&gt;③ 화물을 적재할 때 하중이 치우치지 않게 하는 것도 맞다.&lt;br&gt;④ 승차석이 아닌 위치에 사람을 태우지 않는 것도 맞다.</t>
         </is>
       </c>
       <c r="AI108" s="32" t="inlineStr">
@@ -15360,7 +15364,7 @@
       </c>
       <c r="AH111" s="32" t="inlineStr">
         <is>
-          <t>① R.Q.D 는 암질판별기준이다.&lt;br&gt;② 탄성파속도도 그렇다.&lt;br&gt;④ R.M.R 도 그렇다.</t>
+          <t>① R.Q.D는 암질판별기준이다.&lt;br&gt;② 탄성파속도도 그렇다.&lt;br&gt;④ R.M.R 도 그렇다.</t>
         </is>
       </c>
       <c r="AI111" s="32" t="inlineStr">
@@ -15617,17 +15621,17 @@
       </c>
       <c r="AG113" s="32" t="inlineStr">
         <is>
-          <t>기울기 1 : 0.5 는 &lt;strong&gt;높이 1 에 밑변 0.5&lt;/strong&gt;다. $L = 5 \times 0.5 = 2.5$ [m] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;굴착면 기울기의 읽는 법&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1 : 0.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 1 : 밑변 0.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;앞이 높이, 뒤가 밑변&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 5 [m] × 0.5 = 2.5 [m]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1 : 1.0&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이와 밑변이 같다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;연암 · 풍화암&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1 : 1.8&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;밑변이 훨씬 길다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;모래&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>기울기 1 : 0.5는 &lt;strong&gt;높이 1에 밑변 0.5&lt;/strong&gt;다. $L = 5 \times 0.5 = 2.5$ [m]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;굴착면 기울기의 읽는 법&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1 : 0.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 1 : 밑변 0.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;앞이 높이, 뒤가 밑변&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이 5 [m] × 0.5 = 2.5 [m]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1 : 1.0&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;높이와 밑변이 같다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;연암 · 풍화암&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1 : 1.8&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;밑변이 훨씬 길다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;모래&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH113" s="32" t="inlineStr">
         <is>
-          <t>① 2 [m] 는 계산과 맞지 않는다.&lt;br&gt;③ 5 [m] 는 기울기를 1 : 1 로 본 값이다.&lt;br&gt;④ 10 [m] 는 비를 거꾸로 쓴 값이다.</t>
+          <t>① 2 [m]는 계산과 맞지 않는다.&lt;br&gt;③ 5 [m]는 기울기를 1 : 1로 본 값이다.&lt;br&gt;④ 10 [m]는 비를 거꾸로 쓴 값이다.</t>
         </is>
       </c>
       <c r="AI113" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;굴착면의 기울기&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「1 : 0.5」에서 앞의 1 이 높이&lt;/strong&gt;다 — &lt;strong&gt;뒤집어 읽으면 10 [m] 가 나와 ④로 끌린다&lt;/strong&gt;. &lt;strong&gt;뒤의 수가 작을수록 가파르다&lt;/strong&gt;는 감각으로 확인한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;앞이 높이, 뒤가 밑변&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;굴착면의 기울기&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「1 : 0.5」에서 앞의 1이 높이&lt;/strong&gt;다 — &lt;strong&gt;뒤집어 읽으면 10 [m]가 나와 ④로 끌린다&lt;/strong&gt;. &lt;strong&gt;뒤의 수가 작을수록 가파르다&lt;/strong&gt;는 감각으로 확인한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;앞이 높이, 뒤가 밑변&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15756,7 +15760,7 @@
       </c>
       <c r="AI114" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;선박승강설비&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「300 · 55 · 82」&lt;/strong&gt; 세 숫자다 — &lt;strong&gt;톤수만 300 에서 400 으로 바꿔 놓는 것&lt;/strong&gt;이 이 유형의 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;300톤급 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;선박승강설비&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「300 · 55 · 82」&lt;/strong&gt; 세 숫자다 — &lt;strong&gt;톤수만 300에서 400으로 바꿔 놓는 것&lt;/strong&gt;이 이 유형의 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;300톤급 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15875,7 +15879,7 @@
       </c>
       <c r="AG115" s="32" t="inlineStr">
         <is>
-          <t>난간대는 &lt;strong&gt;지름 2.7 [cm] 이상&lt;/strong&gt; 이라야 한다. &lt;strong&gt;「1.5 [cm]」가 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전난간의 구조&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;부재&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;상부 난간대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바닥에서 90 [cm] 이상 120 [cm] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;120 [cm] 를 넘으면 중간 난간대를 60 [cm] 이내마다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;중간 난간대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상부 난간대와 바닥의 중간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발끝막이판&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바닥에서 10 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난간기둥&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상부 난간대와 중간 난간대를 견고하게 떠받칠 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난간대의 지름&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.7 [cm] 이상의 금속제 파이프&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「1.5 [cm]」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;임의의 방향으로 100 [kg] 이상에 견딜 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>난간대는 &lt;strong&gt;지름 2.7 [cm] 이상&lt;/strong&gt;이라야 한다. &lt;strong&gt;「1.5 [cm]」가 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전난간의 구조&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;부재&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;상부 난간대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바닥에서 90 [cm] 이상 120 [cm] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;120 [cm]를 넘으면 중간 난간대를 60 [cm] 이내마다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;중간 난간대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상부 난간대와 바닥의 중간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발끝막이판&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바닥에서 10 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난간기둥&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상부 난간대와 중간 난간대를 견고하게 떠받칠 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난간대의 지름&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.7 [cm] 이상의 금속제 파이프&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「1.5 [cm]」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;임의의 방향으로 100 [kg] 이상에 견딜 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH115" s="32" t="inlineStr">
@@ -15885,7 +15889,7 @@
       </c>
       <c r="AI115" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전난간의 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「90 ~ 120 · 60 · 10 · 2.7 · 100」&lt;/strong&gt; 다섯 숫자다 — &lt;strong&gt;2.7 [cm] 는 손으로 쥘 만한 굵기&lt;/strong&gt;라 1.5 [cm] 로는 잡기도 어렵고 휘어진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;난간대는 지름 2.7 [cm] 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;안전난간의 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「90 ~ 120 · 60 · 10 · 2.7 · 100」&lt;/strong&gt; 다섯 숫자다 — &lt;strong&gt;2.7 [cm]는 손으로 쥘 만한 굵기&lt;/strong&gt;라 1.5 [cm] 로는 잡기도 어렵고 휘어진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;난간대는 지름 2.7 [cm] 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -16138,7 +16142,7 @@
       </c>
       <c r="AH117" s="32" t="inlineStr">
         <is>
-          <t>① 7 [m/s] 는 기준에 못 미친다.&lt;br&gt;③ 14 [m/s] 는 기준보다 높다.&lt;br&gt;④ 17 [m/s] 도 그렇다.</t>
+          <t>① 7 [m/s]는 기준에 못 미친다.&lt;br&gt;③ 14 [m/s]는 기준보다 높다.&lt;br&gt;④ 17 [m/s] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI117" s="32" t="inlineStr">
@@ -16356,25 +16360,25 @@
       <c r="W119" s="32" t="inlineStr"/>
       <c r="X119" s="32" t="inlineStr">
         <is>
-          <t>초당 10m 를 초과</t>
+          <t>초당 10m를 초과</t>
         </is>
       </c>
       <c r="Y119" s="32" t="inlineStr"/>
       <c r="Z119" s="32" t="inlineStr">
         <is>
-          <t>초당 15m 를 초과</t>
+          <t>초당 15m를 초과</t>
         </is>
       </c>
       <c r="AA119" s="32" t="inlineStr"/>
       <c r="AB119" s="32" t="inlineStr">
         <is>
-          <t>초당 20m 를 초과</t>
+          <t>초당 20m를 초과</t>
         </is>
       </c>
       <c r="AC119" s="32" t="inlineStr"/>
       <c r="AD119" s="32" t="inlineStr">
         <is>
-          <t>초당 30m 를 초과</t>
+          <t>초당 30m를 초과</t>
         </is>
       </c>
       <c r="AE119" s="32" t="inlineStr"/>
@@ -16393,7 +16397,7 @@
       </c>
       <c r="AI119" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;강풍 시 작업중지 기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「10 · 15 · 30 · 35」&lt;/strong&gt; 네 숫자다. &lt;strong&gt;운전작업 중지 기준이 20 에서 15 로 낮아졌다&lt;/strong&gt;는 개정을 함께 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;현행은 15 [m/s] 초과&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 타워크레인 운전작업 중지 기준은 &lt;u&gt;2017.3.3 개정&lt;/u&gt;으로 &lt;u&gt;순간풍속 초당 20 [m] 초과에서 15 [m] 초과로&lt;/u&gt; 낮아졌다. 이 문항의 정답 20 [m/s] 는 옛 기준이다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;강풍 시 작업중지 기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「10 · 15 · 30 · 35」&lt;/strong&gt; 네 숫자다. &lt;strong&gt;운전작업 중지 기준이 20에서 15로 낮아졌다&lt;/strong&gt;는 개정을 함께 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;현행은 15 [m/s] 초과&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 타워크레인 운전작업 중지 기준은 &lt;u&gt;2017.3.3 개정&lt;/u&gt;으로 &lt;u&gt;순간풍속 초당 20 [m] 초과에서 15 [m] 초과로&lt;/u&gt; 낮아졌다. 이 문항의 정답 20 [m/s]는 옛 기준이다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -16522,7 +16526,7 @@
       </c>
       <c r="AI120" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;터널공사의 전기발파&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「30 [m]」라는 숫자가 두 곳에 함께 나온다&lt;/strong&gt; — &lt;strong&gt;도통시험을 하는 거리와 발파모선의 길이&lt;/strong&gt;. &lt;strong&gt;그 가운데 하나만 20 으로 낮춰&lt;/strong&gt; 놓았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;발파모선은 30 [m] 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;터널공사의 전기발파&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「30 [m]」라는 숫자가 두 곳에 함께 나온다&lt;/strong&gt; — &lt;strong&gt;도통시험을 하는 거리와 발파모선의 길이&lt;/strong&gt;. &lt;strong&gt;그 가운데 하나만 20으로 낮춰&lt;/strong&gt; 놓았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;발파모선은 30 [m] 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -16646,12 +16650,12 @@
       </c>
       <c r="AH121" s="32" t="inlineStr">
         <is>
-          <t>② 75 [cm] 는 기준에 못 미친다.&lt;br&gt;③ 60 [cm] 도 그렇다.&lt;br&gt;④ 45 [cm] 도 그렇다.</t>
+          <t>② 75 [cm]는 기준에 못 미친다.&lt;br&gt;③ 60 [cm] 도 그렇다.&lt;br&gt;④ 45 [cm] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI121" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;하역작업장의 통로&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;90 [cm] 는 사람이 짐을 들고 지나갈 수 있는 폭&lt;/strong&gt;이다 — &lt;strong&gt;부두는 한쪽이 바다라 좁으면 그대로 빠진다&lt;/strong&gt;. &lt;strong&gt;작업발판의 40 [cm] 와는 다른 자리&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;부두 통로는 폭 90 [cm] 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;하역작업장의 통로&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;90 [cm]는 사람이 짐을 들고 지나갈 수 있는 폭&lt;/strong&gt;이다 — &lt;strong&gt;부두는 한쪽이 바다라 좁으면 그대로 빠진다&lt;/strong&gt;. &lt;strong&gt;작업발판의 40 [cm] 와는 다른 자리&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;부두 통로는 폭 90 [cm] 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
